--- a/data_lake/industry/CFM/SODIMM.xlsx
+++ b/data_lake/industry/CFM/SODIMM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/industry/CFM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F96066DE-41E9-4FD2-BA35-1087D49674E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{992021C6-1D3E-2F41-8FC2-B74C3ABB04B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18020" yWindow="780" windowWidth="17980" windowHeight="20700" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DDR4 SODIMM 4GB 3200" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -71,38 +71,38 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="180" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="181" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -152,81 +152,81 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="2" builtinId="3"/>
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -505,19 +505,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G45"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -540,7 +540,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -563,7 +563,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -586,7 +586,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -609,7 +609,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -632,7 +632,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -655,7 +655,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -678,7 +678,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -701,7 +701,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -724,7 +724,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -747,7 +747,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -770,7 +770,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -793,7 +793,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -816,7 +816,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -839,7 +839,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -862,7 +862,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -885,7 +885,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -908,7 +908,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -931,7 +931,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -954,7 +954,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -977,7 +977,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -1046,7 +1046,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -1069,7 +1069,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -1115,7 +1115,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -1138,7 +1138,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -1161,7 +1161,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -1230,7 +1230,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -1276,7 +1276,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -1322,7 +1322,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -1345,7 +1345,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -1368,7 +1368,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -1391,7 +1391,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -1423,7 +1423,7 @@
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -1432,7 +1432,7 @@
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -1441,7 +1441,7 @@
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -1450,7 +1450,7 @@
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -1467,20 +1467,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9F7D34-9614-456C-B66D-E33AF53643A7}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -1572,7 +1572,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -1618,7 +1618,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -1641,7 +1641,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -1664,7 +1664,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -1687,7 +1687,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -1710,7 +1710,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -1733,7 +1733,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -1802,7 +1802,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -1825,7 +1825,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -1894,7 +1894,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -1917,7 +1917,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -1963,7 +1963,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -1986,7 +1986,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -2009,7 +2009,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -2032,7 +2032,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -2078,7 +2078,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="10">
         <v>46049</v>
       </c>
@@ -2124,7 +2124,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -2147,7 +2147,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -2170,7 +2170,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -2216,7 +2216,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -2239,7 +2239,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -2262,7 +2262,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -2285,7 +2285,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -2354,7 +2354,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -2377,7 +2377,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -2400,7 +2400,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -2423,7 +2423,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -2446,7 +2446,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -2469,7 +2469,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -2561,7 +2561,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -2584,7 +2584,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -2607,7 +2607,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -2630,7 +2630,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -2653,7 +2653,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -2676,7 +2676,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -2696,6 +2696,167 @@
         <v>72</v>
       </c>
       <c r="G53" s="14">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="14">
+        <v>65</v>
+      </c>
+      <c r="F54" s="14">
+        <v>72</v>
+      </c>
+      <c r="G54" s="14">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="14">
+        <v>65</v>
+      </c>
+      <c r="F55" s="14">
+        <v>72</v>
+      </c>
+      <c r="G55" s="14">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="14">
+        <v>65</v>
+      </c>
+      <c r="F56" s="14">
+        <v>72</v>
+      </c>
+      <c r="G56" s="14">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="14">
+        <v>65</v>
+      </c>
+      <c r="F57" s="14">
+        <v>72</v>
+      </c>
+      <c r="G57" s="14">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="14">
+        <v>65</v>
+      </c>
+      <c r="F58" s="14">
+        <v>72</v>
+      </c>
+      <c r="G58" s="14">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="14">
+        <v>65</v>
+      </c>
+      <c r="F59" s="14">
+        <v>72</v>
+      </c>
+      <c r="G59" s="14">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="14">
+        <v>65</v>
+      </c>
+      <c r="F60" s="14">
+        <v>72</v>
+      </c>
+      <c r="G60" s="14">
         <v>70</v>
       </c>
     </row>
@@ -2707,19 +2868,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EA0A4F0-C10D-4632-99CA-14E155280997}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="6.69921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.6640625" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2742,7 +2903,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -2765,7 +2926,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -2788,7 +2949,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -2811,7 +2972,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -2834,7 +2995,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -2857,7 +3018,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -2880,7 +3041,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -2903,7 +3064,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -2926,7 +3087,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -2949,7 +3110,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -2972,7 +3133,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -2995,7 +3156,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -3018,7 +3179,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -3041,7 +3202,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -3064,7 +3225,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -3087,7 +3248,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -3110,7 +3271,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -3133,7 +3294,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -3156,7 +3317,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -3179,7 +3340,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -3202,7 +3363,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -3225,7 +3386,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -3248,7 +3409,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -3271,7 +3432,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -3294,7 +3455,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -3317,7 +3478,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -3340,7 +3501,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="10">
         <v>46049</v>
       </c>
@@ -3363,7 +3524,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -3386,7 +3547,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -3409,7 +3570,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -3432,7 +3593,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -3455,7 +3616,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -3478,7 +3639,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -3501,7 +3662,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -3524,7 +3685,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -3547,7 +3708,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -3570,7 +3731,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -3593,7 +3754,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -3616,7 +3777,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -3639,7 +3800,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -3662,7 +3823,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -3685,7 +3846,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -3708,7 +3869,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -3731,7 +3892,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -3754,7 +3915,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -3777,7 +3938,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -3800,7 +3961,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -3823,7 +3984,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -3846,7 +4007,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -3869,7 +4030,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -3892,7 +4053,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -3915,7 +4076,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -3935,6 +4096,167 @@
         <v>165</v>
       </c>
       <c r="G53" s="11">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="11">
+        <v>145</v>
+      </c>
+      <c r="F54" s="11">
+        <v>165</v>
+      </c>
+      <c r="G54" s="11">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="11">
+        <v>145</v>
+      </c>
+      <c r="F55" s="11">
+        <v>165</v>
+      </c>
+      <c r="G55" s="11">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="11">
+        <v>145</v>
+      </c>
+      <c r="F56" s="11">
+        <v>165</v>
+      </c>
+      <c r="G56" s="11">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="11">
+        <v>145</v>
+      </c>
+      <c r="F57" s="11">
+        <v>165</v>
+      </c>
+      <c r="G57" s="11">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="11">
+        <v>145</v>
+      </c>
+      <c r="F58" s="11">
+        <v>165</v>
+      </c>
+      <c r="G58" s="11">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="11">
+        <v>145</v>
+      </c>
+      <c r="F59" s="11">
+        <v>165</v>
+      </c>
+      <c r="G59" s="11">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="11">
+        <v>145</v>
+      </c>
+      <c r="F60" s="11">
+        <v>165</v>
+      </c>
+      <c r="G60" s="11">
         <v>155</v>
       </c>
     </row>
@@ -3946,20 +4268,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5297F85F-0123-4AD4-9FF2-92367D502EFD}">
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.8984375" style="22" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" style="22" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.5" style="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.59765625" style="23" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.8984375" style="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="23" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.83203125" style="24" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6" style="25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" style="25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.19921875" style="25" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.796875" style="21"/>
+    <col min="6" max="6" width="6.33203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.1640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.83203125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -3982,7 +4304,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="22">
         <v>46161</v>
       </c>
@@ -4005,7 +4327,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="22">
         <v>46168</v>
       </c>
@@ -4028,7 +4350,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="22">
         <v>46175</v>
       </c>
@@ -4051,7 +4373,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="22">
         <v>46182</v>
       </c>
@@ -4074,7 +4396,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="22">
         <v>46189</v>
       </c>
@@ -4097,7 +4419,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="22">
         <v>46196</v>
       </c>
@@ -4120,7 +4442,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="22">
         <v>46203</v>
       </c>
@@ -4143,7 +4465,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="22">
         <v>46210</v>
       </c>
@@ -4166,7 +4488,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="22">
         <v>46217</v>
       </c>
@@ -4189,7 +4511,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="22">
         <v>46224</v>
       </c>
@@ -4212,7 +4534,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="22">
         <v>46231</v>
       </c>
@@ -4235,7 +4557,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="22">
         <v>46238</v>
       </c>
@@ -4256,6 +4578,167 @@
       </c>
       <c r="G13" s="25">
         <v>115</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="22">
+        <v>46245</v>
+      </c>
+      <c r="B14" s="22">
+        <v>46245</v>
+      </c>
+      <c r="C14" s="23">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="25">
+        <v>110</v>
+      </c>
+      <c r="F14" s="25">
+        <v>125</v>
+      </c>
+      <c r="G14" s="25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="22">
+        <v>46252</v>
+      </c>
+      <c r="B15" s="22">
+        <v>46252</v>
+      </c>
+      <c r="C15" s="23">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="25">
+        <v>110</v>
+      </c>
+      <c r="F15" s="25">
+        <v>125</v>
+      </c>
+      <c r="G15" s="25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="22">
+        <v>46259</v>
+      </c>
+      <c r="B16" s="22">
+        <v>46259</v>
+      </c>
+      <c r="C16" s="23">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="25">
+        <v>110</v>
+      </c>
+      <c r="F16" s="25">
+        <v>125</v>
+      </c>
+      <c r="G16" s="25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="22">
+        <v>46266</v>
+      </c>
+      <c r="B17" s="22">
+        <v>46266</v>
+      </c>
+      <c r="C17" s="23">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="25">
+        <v>110</v>
+      </c>
+      <c r="F17" s="25">
+        <v>125</v>
+      </c>
+      <c r="G17" s="25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="22">
+        <v>46273</v>
+      </c>
+      <c r="B18" s="22">
+        <v>46273</v>
+      </c>
+      <c r="C18" s="23">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="25">
+        <v>113</v>
+      </c>
+      <c r="F18" s="25">
+        <v>128</v>
+      </c>
+      <c r="G18" s="25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="22">
+        <v>46280</v>
+      </c>
+      <c r="B19" s="22">
+        <v>46280</v>
+      </c>
+      <c r="C19" s="23">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="25">
+        <v>115</v>
+      </c>
+      <c r="F19" s="25">
+        <v>130</v>
+      </c>
+      <c r="G19" s="25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="22">
+        <v>46287</v>
+      </c>
+      <c r="B20" s="22">
+        <v>46287</v>
+      </c>
+      <c r="C20" s="23">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="25">
+        <v>115</v>
+      </c>
+      <c r="F20" s="25">
+        <v>130</v>
+      </c>
+      <c r="G20" s="25">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -4266,20 +4749,20 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E39172B4-D2A0-49CA-B32F-E92273A8EC79}">
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="16" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.796875" style="5"/>
+    <col min="8" max="16384" width="8.83203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4302,7 +4785,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="10">
         <v>46161</v>
       </c>
@@ -4325,7 +4808,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="10">
         <v>46168</v>
       </c>
@@ -4348,7 +4831,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="10">
         <v>46175</v>
       </c>
@@ -4371,7 +4854,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="10">
         <v>46182</v>
       </c>
@@ -4394,7 +4877,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="10">
         <v>46189</v>
       </c>
@@ -4417,7 +4900,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="10">
         <v>46196</v>
       </c>
@@ -4440,7 +4923,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="10">
         <v>46203</v>
       </c>
@@ -4463,7 +4946,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="10">
         <v>46210</v>
       </c>
@@ -4486,7 +4969,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="10">
         <v>46217</v>
       </c>
@@ -4509,7 +4992,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="10">
         <v>46224</v>
       </c>
@@ -4532,7 +5015,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
         <v>46231</v>
       </c>
@@ -4555,7 +5038,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="10">
         <v>46238</v>
       </c>
@@ -4576,6 +5059,167 @@
       </c>
       <c r="G13" s="16">
         <v>232</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B14" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C14" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="16">
+        <v>227</v>
+      </c>
+      <c r="F14" s="16">
+        <v>242</v>
+      </c>
+      <c r="G14" s="16">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B15" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C15" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="16">
+        <v>230</v>
+      </c>
+      <c r="F15" s="16">
+        <v>245</v>
+      </c>
+      <c r="G15" s="16">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B16" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C16" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="16">
+        <v>230</v>
+      </c>
+      <c r="F16" s="16">
+        <v>245</v>
+      </c>
+      <c r="G16" s="16">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B17" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C17" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="16">
+        <v>230</v>
+      </c>
+      <c r="F17" s="16">
+        <v>245</v>
+      </c>
+      <c r="G17" s="16">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B18" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C18" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="16">
+        <v>235</v>
+      </c>
+      <c r="F18" s="16">
+        <v>250</v>
+      </c>
+      <c r="G18" s="16">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B19" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C19" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="16">
+        <v>237</v>
+      </c>
+      <c r="F19" s="16">
+        <v>252</v>
+      </c>
+      <c r="G19" s="16">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B20" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C20" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="16">
+        <v>237</v>
+      </c>
+      <c r="F20" s="16">
+        <v>252</v>
+      </c>
+      <c r="G20" s="16">
+        <v>242</v>
       </c>
     </row>
   </sheetData>
